--- a/diseases/d042/2000-2004.xlsx
+++ b/diseases/d042/2000-2004.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -5157,9 +5154,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -10881,9 +10875,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -16605,9 +16596,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -22327,9 +22315,6 @@
         <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
